--- a/exports_hebdomadaires/export_2026-07-06.xlsx
+++ b/exports_hebdomadaires/export_2026-07-06.xlsx
@@ -967,6 +967,11 @@
           <t>EMY-500409</t>
         </is>
       </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>MAC-018</t>
+        </is>
+      </c>
       <c r="AE4" t="inlineStr">
         <is>
           <t>Amine absent (congés du 1er au 19 juillet). Fin de stage de Lucie.</t>
@@ -1948,6 +1953,11 @@
           <t>EMY-500120</t>
         </is>
       </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>MAC-017</t>
+        </is>
+      </c>
       <c r="AE12" t="inlineStr">
         <is>
           <t>Amine absent (congés du 1er au 19 juillet). Fin de stage de Lucie.</t>
@@ -7411,6 +7421,11 @@
           <t>EMY-500755</t>
         </is>
       </c>
+      <c r="AD58" t="inlineStr">
+        <is>
+          <t>MAC-017</t>
+        </is>
+      </c>
       <c r="AE58" t="inlineStr">
         <is>
           <t>Amine absent (congés du 1er au 19 juillet). Fin de stage de Lucie.</t>
@@ -16704,6 +16719,11 @@
           <t>EMY-500597</t>
         </is>
       </c>
+      <c r="AD136" t="inlineStr">
+        <is>
+          <t>MAC-017</t>
+        </is>
+      </c>
       <c r="AE136" t="inlineStr">
         <is>
           <t>Amine absent (congés du 1er au 19 juillet). Fin de stage de Lucie.</t>
@@ -18042,6 +18062,11 @@
           <t>EMY-500162</t>
         </is>
       </c>
+      <c r="AD147" t="inlineStr">
+        <is>
+          <t>MAC-017</t>
+        </is>
+      </c>
       <c r="AE147" t="inlineStr">
         <is>
           <t>Amine absent (congés du 1er au 19 juillet). Fin de stage de Lucie.</t>
@@ -21260,6 +21285,11 @@
           <t>EMY-500208</t>
         </is>
       </c>
+      <c r="AD174" t="inlineStr">
+        <is>
+          <t>MAC-018</t>
+        </is>
+      </c>
       <c r="AE174" t="inlineStr">
         <is>
           <t>Amine absent (congés du 1er au 19 juillet). Fin de stage de Lucie.</t>
@@ -22775,6 +22805,11 @@
           <t>EMY-500354</t>
         </is>
       </c>
+      <c r="AD187" t="inlineStr">
+        <is>
+          <t>MAC-017</t>
+        </is>
+      </c>
       <c r="AE187" t="inlineStr">
         <is>
           <t>Amine absent (congés du 1er au 19 juillet). Fin de stage de Lucie.</t>
@@ -25148,6 +25183,11 @@
           <t>EMY-500818</t>
         </is>
       </c>
+      <c r="AD207" t="inlineStr">
+        <is>
+          <t>MAC-018</t>
+        </is>
+      </c>
       <c r="AE207" t="inlineStr">
         <is>
           <t>Amine absent (congés du 1er au 19 juillet). Fin de stage de Lucie.</t>
@@ -28000,6 +28040,11 @@
           <t>EMY-500555</t>
         </is>
       </c>
+      <c r="AD231" t="inlineStr">
+        <is>
+          <t>MAC-018</t>
+        </is>
+      </c>
       <c r="AE231" t="inlineStr">
         <is>
           <t>Amine absent (congés du 1er au 19 juillet). Fin de stage de Lucie.</t>
@@ -35114,6 +35159,11 @@
           <t>EMY-500266</t>
         </is>
       </c>
+      <c r="AD291" t="inlineStr">
+        <is>
+          <t>MAC-017</t>
+        </is>
+      </c>
       <c r="AE291" t="inlineStr">
         <is>
           <t>Amine absent (congés du 1er au 19 juillet). Fin de stage de Lucie.</t>
@@ -35940,6 +35990,11 @@
           <t>EMY-500803</t>
         </is>
       </c>
+      <c r="AD298" t="inlineStr">
+        <is>
+          <t>MAC-018</t>
+        </is>
+      </c>
       <c r="AE298" t="inlineStr">
         <is>
           <t>Amine absent (congés du 1er au 19 juillet). Fin de stage de Lucie.</t>
@@ -37226,6 +37281,11 @@
           <t>EMY-500237</t>
         </is>
       </c>
+      <c r="AD308" t="inlineStr">
+        <is>
+          <t>MAC-017</t>
+        </is>
+      </c>
       <c r="AE308" t="inlineStr">
         <is>
           <t>Amine absent (congés du 1er au 19 juillet). Fin de stage de Lucie.</t>
@@ -37340,6 +37400,11 @@
           <t>EMY-500420</t>
         </is>
       </c>
+      <c r="AD309" t="inlineStr">
+        <is>
+          <t>MAC-017</t>
+        </is>
+      </c>
       <c r="AE309" t="inlineStr">
         <is>
           <t>Amine absent (congés du 1er au 19 juillet). Fin de stage de Lucie.</t>
@@ -38378,6 +38443,11 @@
           <t>EMY-500354</t>
         </is>
       </c>
+      <c r="AD318" t="inlineStr">
+        <is>
+          <t>MAC-017</t>
+        </is>
+      </c>
       <c r="AE318" t="inlineStr">
         <is>
           <t>Amine absent (congés du 1er au 19 juillet). Fin de stage de Lucie.</t>
@@ -41981,6 +42051,11 @@
           <t>EMY-500476</t>
         </is>
       </c>
+      <c r="AD348" t="inlineStr">
+        <is>
+          <t>MAC-017</t>
+        </is>
+      </c>
       <c r="AE348" t="inlineStr">
         <is>
           <t>Amine absent (congés du 1er au 19 juillet). Fin de stage de Lucie.</t>
@@ -45968,6 +46043,11 @@
           <t>EMY-500013</t>
         </is>
       </c>
+      <c r="AD382" t="inlineStr">
+        <is>
+          <t>MAC-017</t>
+        </is>
+      </c>
       <c r="AE382" t="inlineStr">
         <is>
           <t>Amine absent (congés du 1er au 19 juillet). Fin de stage de Lucie.</t>
@@ -46442,6 +46522,11 @@
           <t>EMY-500796</t>
         </is>
       </c>
+      <c r="AD386" t="inlineStr">
+        <is>
+          <t>MAC-017</t>
+        </is>
+      </c>
       <c r="AE386" t="inlineStr">
         <is>
           <t>Amine absent (congés du 1er au 19 juillet). Fin de stage de Lucie.</t>
@@ -52197,6 +52282,11 @@
           <t>EMY-500278</t>
         </is>
       </c>
+      <c r="AD435" t="inlineStr">
+        <is>
+          <t>MAC-018</t>
+        </is>
+      </c>
       <c r="AE435" t="inlineStr">
         <is>
           <t>Amine absent (congés du 1er au 19 juillet). Fin de stage de Lucie.</t>
@@ -52653,6 +52743,11 @@
           <t>EMY-500755</t>
         </is>
       </c>
+      <c r="AD439" t="inlineStr">
+        <is>
+          <t>MAC-017</t>
+        </is>
+      </c>
       <c r="AE439" t="inlineStr">
         <is>
           <t>Amine absent (congés du 1er au 19 juillet). Fin de stage de Lucie.</t>
@@ -56337,6 +56432,11 @@
           <t>EMY-500527</t>
         </is>
       </c>
+      <c r="AD470" t="inlineStr">
+        <is>
+          <t>MAC-018</t>
+        </is>
+      </c>
       <c r="AE470" t="inlineStr">
         <is>
           <t>Amine absent (congés du 1er au 19 juillet). Fin de stage de Lucie.</t>
@@ -58019,6 +58119,11 @@
           <t>EMY-500476</t>
         </is>
       </c>
+      <c r="AD484" t="inlineStr">
+        <is>
+          <t>MAC-017</t>
+        </is>
+      </c>
       <c r="AE484" t="inlineStr">
         <is>
           <t>Amine absent (congés du 1er au 19 juillet). Fin de stage de Lucie.</t>
@@ -58466,6 +58571,11 @@
           <t>EMY-500476</t>
         </is>
       </c>
+      <c r="AD488" t="inlineStr">
+        <is>
+          <t>MAC-017</t>
+        </is>
+      </c>
       <c r="AE488" t="inlineStr">
         <is>
           <t>Amine absent (congés du 1er au 19 juillet). Fin de stage de Lucie.</t>
@@ -59259,6 +59369,11 @@
           <t>EMY-500162</t>
         </is>
       </c>
+      <c r="AD495" t="inlineStr">
+        <is>
+          <t>MAC-017</t>
+        </is>
+      </c>
       <c r="AE495" t="inlineStr">
         <is>
           <t>Amine absent (congés du 1er au 19 juillet). Fin de stage de Lucie.</t>
@@ -61987,6 +62102,11 @@
           <t>EMY-500166</t>
         </is>
       </c>
+      <c r="AD518" t="inlineStr">
+        <is>
+          <t>MAC-017</t>
+        </is>
+      </c>
       <c r="AE518" t="inlineStr">
         <is>
           <t>Amine absent (congés du 1er au 19 juillet). Fin de stage de Lucie.</t>
@@ -64210,6 +64330,11 @@
           <t>EMY-500162</t>
         </is>
       </c>
+      <c r="AD537" t="inlineStr">
+        <is>
+          <t>MAC-017</t>
+        </is>
+      </c>
       <c r="AE537" t="inlineStr">
         <is>
           <t>Amine absent (congés du 1er au 19 juillet). Fin de stage de Lucie.</t>
@@ -65100,6 +65225,11 @@
           <t>EMY-500803</t>
         </is>
       </c>
+      <c r="AD544" t="inlineStr">
+        <is>
+          <t>MAC-018</t>
+        </is>
+      </c>
       <c r="AE544" t="inlineStr">
         <is>
           <t>Amine absent (congés du 1er au 19 juillet). Fin de stage de Lucie.</t>
@@ -65677,6 +65807,11 @@
           <t>EMY-500395</t>
         </is>
       </c>
+      <c r="AD549" t="inlineStr">
+        <is>
+          <t>MAC-017</t>
+        </is>
+      </c>
       <c r="AE549" t="inlineStr">
         <is>
           <t>Amine absent (congés du 1er au 19 juillet). Fin de stage de Lucie.</t>
@@ -67119,6 +67254,11 @@
           <t>EMY-500793</t>
         </is>
       </c>
+      <c r="AD561" t="inlineStr">
+        <is>
+          <t>MAC-018</t>
+        </is>
+      </c>
       <c r="AE561" t="inlineStr">
         <is>
           <t>Amine absent (congés du 1er au 19 juillet). Fin de stage de Lucie.</t>
@@ -69227,6 +69367,11 @@
           <t>EMY-500825</t>
         </is>
       </c>
+      <c r="AD579" t="inlineStr">
+        <is>
+          <t>MAC-017</t>
+        </is>
+      </c>
       <c r="AE579" t="inlineStr">
         <is>
           <t>Amine absent (congés du 1er au 19 juillet). Fin de stage de Lucie.</t>
@@ -70288,6 +70433,11 @@
           <t>EMY-500721</t>
         </is>
       </c>
+      <c r="AD588" t="inlineStr">
+        <is>
+          <t>MAC-018</t>
+        </is>
+      </c>
       <c r="AE588" t="inlineStr">
         <is>
           <t>Amine absent (congés du 1er au 19 juillet). Fin de stage de Lucie.</t>
@@ -71364,6 +71514,11 @@
           <t>EMY-500241</t>
         </is>
       </c>
+      <c r="AD597" t="inlineStr">
+        <is>
+          <t>MAC-017</t>
+        </is>
+      </c>
       <c r="AE597" t="inlineStr">
         <is>
           <t>Amine absent (congés du 1er au 19 juillet). Fin de stage de Lucie.</t>
@@ -71719,6 +71874,11 @@
           <t>EMY-500013</t>
         </is>
       </c>
+      <c r="AD600" t="inlineStr">
+        <is>
+          <t>MAC-017</t>
+        </is>
+      </c>
       <c r="AE600" t="inlineStr">
         <is>
           <t>Amine absent (congés du 1er au 19 juillet). Fin de stage de Lucie.</t>
@@ -74631,6 +74791,11 @@
           <t>EMY-500114</t>
         </is>
       </c>
+      <c r="AD625" t="inlineStr">
+        <is>
+          <t>MAC-018</t>
+        </is>
+      </c>
       <c r="AE625" t="inlineStr">
         <is>
           <t>Amine absent (congés du 1er au 19 juillet). Fin de stage de Lucie.</t>
@@ -75338,6 +75503,11 @@
           <t>EMY-500342</t>
         </is>
       </c>
+      <c r="AD631" t="inlineStr">
+        <is>
+          <t>MAC-017</t>
+        </is>
+      </c>
       <c r="AE631" t="inlineStr">
         <is>
           <t>Amine absent (congés du 1er au 19 juillet). Fin de stage de Lucie.</t>
@@ -77217,6 +77387,11 @@
           <t>EMY-500796</t>
         </is>
       </c>
+      <c r="AD647" t="inlineStr">
+        <is>
+          <t>MAC-017</t>
+        </is>
+      </c>
       <c r="AE647" t="inlineStr">
         <is>
           <t>Amine absent (congés du 1er au 19 juillet). Fin de stage de Lucie.</t>
@@ -78763,6 +78938,11 @@
           <t>EMY-500755</t>
         </is>
       </c>
+      <c r="AD660" t="inlineStr">
+        <is>
+          <t>MAC-017</t>
+        </is>
+      </c>
       <c r="AE660" t="inlineStr">
         <is>
           <t>Amine absent (congés du 1er au 19 juillet). Fin de stage de Lucie.</t>
@@ -79951,6 +80131,11 @@
           <t>EMY-500395</t>
         </is>
       </c>
+      <c r="AD670" t="inlineStr">
+        <is>
+          <t>MAC-017</t>
+        </is>
+      </c>
       <c r="AE670" t="inlineStr">
         <is>
           <t>Amine absent (congés du 1er au 19 juillet). Fin de stage de Lucie.</t>
@@ -81254,6 +81439,11 @@
       <c r="AC681" t="inlineStr">
         <is>
           <t>EMY-500020</t>
+        </is>
+      </c>
+      <c r="AD681" t="inlineStr">
+        <is>
+          <t>MAC-018</t>
         </is>
       </c>
       <c r="AE681" t="inlineStr">

--- a/exports_hebdomadaires/export_2026-07-06.xlsx
+++ b/exports_hebdomadaires/export_2026-07-06.xlsx
@@ -1029,7 +1029,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG5" t="n">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG9" t="n">
@@ -1792,7 +1792,7 @@
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG12" t="n">
@@ -2111,7 +2111,7 @@
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG15" t="n">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG16" t="n">
@@ -2431,7 +2431,7 @@
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG18" t="n">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG19" t="n">
@@ -2751,7 +2751,7 @@
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG21" t="n">
@@ -3052,7 +3052,7 @@
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG24" t="n">
@@ -3483,7 +3483,7 @@
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG28" t="n">
@@ -3587,7 +3587,7 @@
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG29" t="n">
@@ -3818,7 +3818,7 @@
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG31" t="n">
@@ -4036,7 +4036,7 @@
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG33" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG36" t="n">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG37" t="n">
@@ -4797,7 +4797,7 @@
       </c>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG40" t="n">
@@ -5236,7 +5236,7 @@
       </c>
       <c r="AF44" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG44" t="n">
@@ -5537,7 +5537,7 @@
       </c>
       <c r="AF47" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG47" t="n">
@@ -5765,7 +5765,7 @@
       </c>
       <c r="AF49" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG49" t="n">
@@ -5882,7 +5882,7 @@
       </c>
       <c r="AF50" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG50" t="n">
@@ -6077,7 +6077,7 @@
       </c>
       <c r="AF52" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG52" t="n">
@@ -6756,7 +6756,7 @@
       </c>
       <c r="AF58" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG58" t="n">
@@ -6979,7 +6979,7 @@
       </c>
       <c r="AF60" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG60" t="n">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="AF61" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG61" t="n">
@@ -7319,7 +7319,7 @@
       </c>
       <c r="AF63" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG63" t="n">
@@ -7423,7 +7423,7 @@
       </c>
       <c r="AF64" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG64" t="n">
@@ -7841,7 +7841,7 @@
       </c>
       <c r="AF68" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG68" t="n">
@@ -8057,7 +8057,7 @@
       </c>
       <c r="AF70" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG70" t="n">
@@ -8169,7 +8169,7 @@
       </c>
       <c r="AF71" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG71" t="n">
@@ -8273,7 +8273,7 @@
       </c>
       <c r="AF72" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG72" t="n">
@@ -8572,7 +8572,7 @@
       </c>
       <c r="AF75" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG75" t="n">
@@ -8795,7 +8795,7 @@
       </c>
       <c r="AF77" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG77" t="n">
@@ -8904,7 +8904,7 @@
       </c>
       <c r="AF78" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG78" t="n">
@@ -9122,7 +9122,7 @@
       </c>
       <c r="AF80" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG80" t="n">
@@ -9426,7 +9426,7 @@
       </c>
       <c r="AF83" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG83" t="n">
@@ -9973,7 +9973,7 @@
       </c>
       <c r="AF88" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG88" t="n">
@@ -10437,7 +10437,7 @@
       </c>
       <c r="AF92" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG92" t="n">
@@ -10962,7 +10962,7 @@
       </c>
       <c r="AF97" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG97" t="n">
@@ -11071,7 +11071,7 @@
       </c>
       <c r="AF98" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG98" t="n">
@@ -11175,7 +11175,7 @@
       </c>
       <c r="AF99" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG99" t="n">
@@ -11284,7 +11284,7 @@
       </c>
       <c r="AF100" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG100" t="n">
@@ -11396,7 +11396,7 @@
       </c>
       <c r="AF101" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG101" t="n">
@@ -11505,7 +11505,7 @@
       </c>
       <c r="AF102" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG102" t="n">
@@ -11900,7 +11900,7 @@
       </c>
       <c r="AF106" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG106" t="n">
@@ -12295,7 +12295,7 @@
       </c>
       <c r="AF110" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG110" t="n">
@@ -12736,7 +12736,7 @@
       </c>
       <c r="AF114" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG114" t="n">
@@ -13478,7 +13478,7 @@
       </c>
       <c r="AF121" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG121" t="n">
@@ -13919,7 +13919,7 @@
       </c>
       <c r="AF125" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG125" t="n">
@@ -14031,7 +14031,7 @@
       </c>
       <c r="AF126" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG126" t="n">
@@ -14236,7 +14236,7 @@
       </c>
       <c r="AF128" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG128" t="n">
@@ -14452,7 +14452,7 @@
       </c>
       <c r="AF130" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG130" t="n">
@@ -14561,7 +14561,7 @@
       </c>
       <c r="AF131" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG131" t="n">
@@ -15382,7 +15382,7 @@
       </c>
       <c r="AF139" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG139" t="n">
@@ -16068,7 +16068,7 @@
       </c>
       <c r="AF145" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG145" t="n">
@@ -16395,7 +16395,7 @@
       </c>
       <c r="AF148" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG148" t="n">
@@ -16499,7 +16499,7 @@
       </c>
       <c r="AF149" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG149" t="n">
@@ -16712,7 +16712,7 @@
       </c>
       <c r="AF151" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG151" t="n">
@@ -17277,7 +17277,7 @@
       </c>
       <c r="AF156" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG156" t="n">
@@ -17506,7 +17506,7 @@
       </c>
       <c r="AF158" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG158" t="n">
@@ -17618,7 +17618,7 @@
       </c>
       <c r="AF159" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG159" t="n">
@@ -17826,7 +17826,7 @@
       </c>
       <c r="AF161" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG161" t="n">
@@ -17930,7 +17930,7 @@
       </c>
       <c r="AF162" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG162" t="n">
@@ -18034,7 +18034,7 @@
       </c>
       <c r="AF163" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG163" t="n">
@@ -18553,7 +18553,7 @@
       </c>
       <c r="AF168" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG168" t="n">
@@ -19707,7 +19707,7 @@
       </c>
       <c r="AF179" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG179" t="n">
@@ -19811,7 +19811,7 @@
       </c>
       <c r="AF180" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG180" t="n">
@@ -20125,7 +20125,7 @@
       </c>
       <c r="AF183" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG183" t="n">
@@ -20338,7 +20338,7 @@
       </c>
       <c r="AF185" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG185" t="n">
@@ -20574,7 +20574,7 @@
       </c>
       <c r="AF187" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG187" t="n">
@@ -20691,7 +20691,7 @@
       </c>
       <c r="AF188" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG188" t="n">
@@ -21392,7 +21392,7 @@
       </c>
       <c r="AF195" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG195" t="n">
@@ -21962,7 +21962,7 @@
       </c>
       <c r="AF200" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG200" t="n">
@@ -22592,7 +22592,7 @@
       </c>
       <c r="AF206" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG206" t="n">
@@ -22888,7 +22888,7 @@
       </c>
       <c r="AF209" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG209" t="n">
@@ -23416,7 +23416,7 @@
       </c>
       <c r="AF214" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG214" t="n">
@@ -23611,7 +23611,7 @@
       </c>
       <c r="AF216" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG216" t="n">
@@ -23811,7 +23811,7 @@
       </c>
       <c r="AF218" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG218" t="n">
@@ -23915,7 +23915,7 @@
       </c>
       <c r="AF219" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG219" t="n">
@@ -24151,7 +24151,7 @@
       </c>
       <c r="AF221" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG221" t="n">
@@ -24260,7 +24260,7 @@
       </c>
       <c r="AF222" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG222" t="n">
@@ -24364,7 +24364,7 @@
       </c>
       <c r="AF223" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG223" t="n">
@@ -24577,7 +24577,7 @@
       </c>
       <c r="AF225" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG225" t="n">
@@ -25428,7 +25428,7 @@
       </c>
       <c r="AF233" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG233" t="n">
@@ -25757,7 +25757,7 @@
       </c>
       <c r="AF236" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG236" t="n">
@@ -25869,7 +25869,7 @@
       </c>
       <c r="AF237" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG237" t="n">
@@ -26103,7 +26103,7 @@
       </c>
       <c r="AF239" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG239" t="n">
@@ -26521,7 +26521,7 @@
       </c>
       <c r="AF243" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG243" t="n">
@@ -26739,7 +26739,7 @@
       </c>
       <c r="AF245" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG245" t="n">
@@ -27286,7 +27286,7 @@
       </c>
       <c r="AF250" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG250" t="n">
@@ -28175,7 +28175,7 @@
       </c>
       <c r="AF258" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG258" t="n">
@@ -28383,7 +28383,7 @@
       </c>
       <c r="AF260" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG260" t="n">
@@ -29698,7 +29698,7 @@
       </c>
       <c r="AF273" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG273" t="n">
@@ -29802,7 +29802,7 @@
       </c>
       <c r="AF274" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG274" t="n">
@@ -30476,7 +30476,7 @@
       </c>
       <c r="AF280" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG280" t="n">
@@ -31405,7 +31405,7 @@
       </c>
       <c r="AF289" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG289" t="n">
@@ -31522,7 +31522,7 @@
       </c>
       <c r="AF290" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG290" t="n">
@@ -31626,7 +31626,7 @@
       </c>
       <c r="AF291" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG291" t="n">
@@ -32256,7 +32256,7 @@
       </c>
       <c r="AF297" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG297" t="n">
@@ -33146,7 +33146,7 @@
       </c>
       <c r="AF305" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG305" t="n">
@@ -33250,7 +33250,7 @@
       </c>
       <c r="AF306" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG306" t="n">
@@ -33455,7 +33455,7 @@
       </c>
       <c r="AF308" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG308" t="n">
@@ -33564,7 +33564,7 @@
       </c>
       <c r="AF309" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG309" t="n">
@@ -33676,7 +33676,7 @@
       </c>
       <c r="AF310" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG310" t="n">
@@ -33998,7 +33998,7 @@
       </c>
       <c r="AF313" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG313" t="n">
@@ -34353,7 +34353,7 @@
       </c>
       <c r="AF316" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG316" t="n">
@@ -34548,7 +34548,7 @@
       </c>
       <c r="AF318" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG318" t="n">
@@ -34769,7 +34769,7 @@
       </c>
       <c r="AF320" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG320" t="n">
@@ -34990,7 +34990,7 @@
       </c>
       <c r="AF322" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG322" t="n">
@@ -35211,7 +35211,7 @@
       </c>
       <c r="AF324" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG324" t="n">
@@ -35582,7 +35582,7 @@
       </c>
       <c r="AF327" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG327" t="n">
@@ -36269,7 +36269,7 @@
       </c>
       <c r="AF333" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG333" t="n">
@@ -36373,7 +36373,7 @@
       </c>
       <c r="AF334" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG334" t="n">
@@ -37039,7 +37039,7 @@
       </c>
       <c r="AF340" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG340" t="n">
@@ -37262,7 +37262,7 @@
       </c>
       <c r="AF342" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG342" t="n">
@@ -37379,7 +37379,7 @@
       </c>
       <c r="AF343" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG343" t="n">
@@ -38114,7 +38114,7 @@
       </c>
       <c r="AF350" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG350" t="n">
@@ -38218,7 +38218,7 @@
       </c>
       <c r="AF351" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG351" t="n">
@@ -38322,7 +38322,7 @@
       </c>
       <c r="AF352" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG352" t="n">
@@ -38525,7 +38525,7 @@
       </c>
       <c r="AF354" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG354" t="n">
@@ -38852,7 +38852,7 @@
       </c>
       <c r="AF357" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG357" t="n">
@@ -39736,7 +39736,7 @@
       </c>
       <c r="AF365" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG365" t="n">
@@ -39848,7 +39848,7 @@
       </c>
       <c r="AF366" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG366" t="n">
@@ -39952,7 +39952,7 @@
       </c>
       <c r="AF367" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG367" t="n">
@@ -40056,7 +40056,7 @@
       </c>
       <c r="AF368" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG368" t="n">
@@ -40256,7 +40256,7 @@
       </c>
       <c r="AF370" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG370" t="n">
@@ -40365,7 +40365,7 @@
       </c>
       <c r="AF371" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG371" t="n">
@@ -41176,7 +41176,7 @@
       </c>
       <c r="AF378" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG378" t="n">
@@ -42250,7 +42250,7 @@
       </c>
       <c r="AF388" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG388" t="n">
@@ -42569,7 +42569,7 @@
       </c>
       <c r="AF391" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG391" t="n">
@@ -43567,7 +43567,7 @@
       </c>
       <c r="AF400" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG400" t="n">
@@ -43676,7 +43676,7 @@
       </c>
       <c r="AF401" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG401" t="n">
@@ -43785,7 +43785,7 @@
       </c>
       <c r="AF402" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG402" t="n">
@@ -43894,7 +43894,7 @@
       </c>
       <c r="AF403" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG403" t="n">
@@ -44226,7 +44226,7 @@
       </c>
       <c r="AF406" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG406" t="n">
@@ -44335,7 +44335,7 @@
       </c>
       <c r="AF407" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG407" t="n">
@@ -44439,7 +44439,7 @@
       </c>
       <c r="AF408" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG408" t="n">
@@ -44779,7 +44779,7 @@
       </c>
       <c r="AF411" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG411" t="n">
@@ -45263,7 +45263,7 @@
       </c>
       <c r="AF415" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG415" t="n">
@@ -45491,7 +45491,7 @@
       </c>
       <c r="AF417" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG417" t="n">
@@ -45603,7 +45603,7 @@
       </c>
       <c r="AF418" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG418" t="n">
@@ -46016,7 +46016,7 @@
       </c>
       <c r="AF422" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG422" t="n">
@@ -46221,7 +46221,7 @@
       </c>
       <c r="AF424" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG424" t="n">
@@ -46548,7 +46548,7 @@
       </c>
       <c r="AF427" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG427" t="n">
@@ -47497,7 +47497,7 @@
       </c>
       <c r="AF436" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG436" t="n">
@@ -47601,7 +47601,7 @@
       </c>
       <c r="AF437" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG437" t="n">
@@ -47705,7 +47705,7 @@
       </c>
       <c r="AF438" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG438" t="n">
@@ -48323,7 +48323,7 @@
       </c>
       <c r="AF444" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG444" t="n">
@@ -48976,7 +48976,7 @@
       </c>
       <c r="AF450" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG450" t="n">
@@ -49176,7 +49176,7 @@
       </c>
       <c r="AF452" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG452" t="n">
@@ -49280,7 +49280,7 @@
       </c>
       <c r="AF453" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG453" t="n">
@@ -49822,7 +49822,7 @@
       </c>
       <c r="AF458" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG458" t="n">
@@ -50595,7 +50595,7 @@
       </c>
       <c r="AF465" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG465" t="n">
@@ -50808,7 +50808,7 @@
       </c>
       <c r="AF467" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG467" t="n">
@@ -51130,7 +51130,7 @@
       </c>
       <c r="AF470" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG470" t="n">
@@ -51239,7 +51239,7 @@
       </c>
       <c r="AF471" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG471" t="n">
@@ -51348,7 +51348,7 @@
       </c>
       <c r="AF472" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG472" t="n">
@@ -51571,7 +51571,7 @@
       </c>
       <c r="AF474" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG474" t="n">
@@ -51675,7 +51675,7 @@
       </c>
       <c r="AF475" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG475" t="n">
@@ -52126,7 +52126,7 @@
       </c>
       <c r="AF479" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG479" t="n">
@@ -52878,7 +52878,7 @@
       </c>
       <c r="AF486" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG486" t="n">
@@ -52987,7 +52987,7 @@
       </c>
       <c r="AF487" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG487" t="n">
@@ -53104,7 +53104,7 @@
       </c>
       <c r="AF488" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG488" t="n">
@@ -53680,7 +53680,7 @@
       </c>
       <c r="AF493" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG493" t="n">
@@ -53903,7 +53903,7 @@
       </c>
       <c r="AF495" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG495" t="n">
@@ -54220,7 +54220,7 @@
       </c>
       <c r="AF498" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG498" t="n">
@@ -54324,7 +54324,7 @@
       </c>
       <c r="AF499" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG499" t="n">
@@ -54648,7 +54648,7 @@
       </c>
       <c r="AF502" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG502" t="n">
@@ -54856,7 +54856,7 @@
       </c>
       <c r="AF504" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG504" t="n">
@@ -55520,7 +55520,7 @@
       </c>
       <c r="AF510" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG510" t="n">
@@ -55746,7 +55746,7 @@
       </c>
       <c r="AF512" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG512" t="n">
@@ -55850,7 +55850,7 @@
       </c>
       <c r="AF513" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG513" t="n">
@@ -55954,7 +55954,7 @@
       </c>
       <c r="AF514" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG514" t="n">
@@ -56058,7 +56058,7 @@
       </c>
       <c r="AF515" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG515" t="n">
@@ -56167,7 +56167,7 @@
       </c>
       <c r="AF516" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG516" t="n">
@@ -56271,7 +56271,7 @@
       </c>
       <c r="AF517" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG517" t="n">
@@ -56499,7 +56499,7 @@
       </c>
       <c r="AF519" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG519" t="n">
@@ -56894,7 +56894,7 @@
       </c>
       <c r="AF523" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG523" t="n">
@@ -56998,7 +56998,7 @@
       </c>
       <c r="AF524" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG524" t="n">
@@ -57102,7 +57102,7 @@
       </c>
       <c r="AF525" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG525" t="n">
@@ -57206,7 +57206,7 @@
       </c>
       <c r="AF526" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG526" t="n">
@@ -57318,7 +57318,7 @@
       </c>
       <c r="AF527" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG527" t="n">
@@ -57653,7 +57653,7 @@
       </c>
       <c r="AF530" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG530" t="n">
@@ -57988,7 +57988,7 @@
       </c>
       <c r="AF533" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG533" t="n">
@@ -58297,7 +58297,7 @@
       </c>
       <c r="AF536" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG536" t="n">
@@ -59308,7 +59308,7 @@
       </c>
       <c r="AF545" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG545" t="n">
@@ -59627,7 +59627,7 @@
       </c>
       <c r="AF548" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG548" t="n">
@@ -59731,7 +59731,7 @@
       </c>
       <c r="AF549" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG549" t="n">
@@ -59967,7 +59967,7 @@
       </c>
       <c r="AF551" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG551" t="n">
@@ -60076,7 +60076,7 @@
       </c>
       <c r="AF552" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG552" t="n">
@@ -60289,7 +60289,7 @@
       </c>
       <c r="AF554" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG554" t="n">
@@ -60689,7 +60689,7 @@
       </c>
       <c r="AF558" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG558" t="n">
@@ -60798,7 +60798,7 @@
       </c>
       <c r="AF559" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG559" t="n">
@@ -60902,7 +60902,7 @@
       </c>
       <c r="AF560" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG560" t="n">
@@ -61470,7 +61470,7 @@
       </c>
       <c r="AF565" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG565" t="n">
@@ -62397,7 +62397,7 @@
       </c>
       <c r="AF573" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG573" t="n">
@@ -63271,7 +63271,7 @@
       </c>
       <c r="AF581" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG581" t="n">
@@ -63489,7 +63489,7 @@
       </c>
       <c r="AF583" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG583" t="n">
@@ -63821,7 +63821,7 @@
       </c>
       <c r="AF586" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG586" t="n">
@@ -64604,7 +64604,7 @@
       </c>
       <c r="AF593" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG593" t="n">
@@ -65453,7 +65453,7 @@
       </c>
       <c r="AF601" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG601" t="n">
@@ -66479,7 +66479,7 @@
       </c>
       <c r="AF610" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG610" t="n">
@@ -66817,7 +66817,7 @@
       </c>
       <c r="AF613" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG613" t="n">
@@ -67025,7 +67025,7 @@
       </c>
       <c r="AF615" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG615" t="n">
@@ -67858,7 +67858,7 @@
       </c>
       <c r="AF623" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG623" t="n">
@@ -68327,7 +68327,7 @@
       </c>
       <c r="AF627" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG627" t="n">
@@ -68548,7 +68548,7 @@
       </c>
       <c r="AF629" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG629" t="n">
@@ -68844,7 +68844,7 @@
       </c>
       <c r="AF632" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG632" t="n">
@@ -69176,7 +69176,7 @@
       </c>
       <c r="AF635" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG635" t="n">
@@ -69989,7 +69989,7 @@
       </c>
       <c r="AF643" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG643" t="n">
@@ -70106,7 +70106,7 @@
       </c>
       <c r="AF644" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG644" t="n">
@@ -70438,7 +70438,7 @@
       </c>
       <c r="AF647" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG647" t="n">
@@ -70661,7 +70661,7 @@
       </c>
       <c r="AF649" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG649" t="n">
@@ -71175,7 +71175,7 @@
       </c>
       <c r="AF654" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG654" t="n">
@@ -71279,7 +71279,7 @@
       </c>
       <c r="AF655" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG655" t="n">
@@ -71383,7 +71383,7 @@
       </c>
       <c r="AF656" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG656" t="n">
@@ -71591,7 +71591,7 @@
       </c>
       <c r="AF658" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG658" t="n">
@@ -72042,7 +72042,7 @@
       </c>
       <c r="AF662" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG662" t="n">
@@ -72265,7 +72265,7 @@
       </c>
       <c r="AF664" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG664" t="n">
@@ -72369,7 +72369,7 @@
       </c>
       <c r="AF665" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG665" t="n">
@@ -72673,7 +72673,7 @@
       </c>
       <c r="AF668" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG668" t="n">
@@ -72912,7 +72912,7 @@
       </c>
       <c r="AF670" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG670" t="n">
@@ -73148,7 +73148,7 @@
       </c>
       <c r="AF672" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG672" t="n">
@@ -73252,7 +73252,7 @@
       </c>
       <c r="AF673" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG673" t="n">
@@ -73462,7 +73462,7 @@
       </c>
       <c r="AF675" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG675" t="n">
@@ -73896,7 +73896,7 @@
       </c>
       <c r="AF679" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG679" t="n">
@@ -74195,7 +74195,7 @@
       </c>
       <c r="AF682" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG682" t="n">
@@ -74664,7 +74664,7 @@
       </c>
       <c r="AF686" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG686" t="n">
@@ -75102,7 +75102,7 @@
       </c>
       <c r="AF690" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG690" t="n">
